--- a/simulation/dac/dac_economics.xlsx
+++ b/simulation/dac/dac_economics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Propanol production\simulation\dac\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356A5041-FC6B-4C6C-A3DA-60B48DACD18B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5EA77C5-188A-4DB0-B355-436415A98957}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="495" windowWidth="21600" windowHeight="8430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
